--- a/exports/BANKBARODA_full_report.xlsx
+++ b/exports/BANKBARODA_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q66"/>
+  <dimension ref="A1:U66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,19 +557,19 @@
         <v>7.79</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>44613.38541666666</v>
+        <v>44613.55208333334</v>
       </c>
       <c r="H2" t="n">
-        <v>91.55</v>
+        <v>90.2</v>
       </c>
       <c r="I2" t="n">
         <v>90.89580120088371</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>42</v>
+        <v>42.16666666666666</v>
       </c>
       <c r="K2" t="n">
-        <v>17.75</v>
+        <v>16.01</v>
       </c>
       <c r="L2" t="n">
         <v>3.34</v>
@@ -564,7 +587,19 @@
         <v>1</v>
       </c>
       <c r="Q2" t="n">
-        <v>59</v>
+        <v>60</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -591,25 +626,25 @@
         <v>10.12</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>44629.55208333334</v>
+        <v>44630.38541666666</v>
       </c>
       <c r="H3" t="n">
-        <v>85.34999999999999</v>
+        <v>89.75</v>
       </c>
       <c r="I3" t="n">
         <v>89.018298244926</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>16</v>
+        <v>16.83333333333333</v>
       </c>
       <c r="K3" t="n">
-        <v>5.38</v>
+        <v>0.5</v>
       </c>
       <c r="L3" t="n">
         <v>5.21</v>
       </c>
       <c r="M3" t="n">
-        <v>3.68</v>
+        <v>3.81</v>
       </c>
       <c r="N3" t="n">
         <v>6.95</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2</v>
+      </c>
+      <c r="U3" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -648,19 +695,19 @@
         <v>11.42</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>44664.55208333334</v>
+        <v>44669.38541666666</v>
       </c>
       <c r="H4" t="n">
-        <v>104.5</v>
+        <v>99.45</v>
       </c>
       <c r="I4" t="n">
         <v>99.77896066899699</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>34.16666666666666</v>
+        <v>39</v>
       </c>
       <c r="K4" t="n">
-        <v>16.43</v>
+        <v>10.81</v>
       </c>
       <c r="L4" t="n">
         <v>2.56</v>
@@ -669,7 +716,7 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="N4" t="n">
-        <v>1.49</v>
+        <v>4.55</v>
       </c>
       <c r="O4" t="n">
         <v>2.93</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>9.98</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>44713.38541666666</v>
+        <v>44713.55208333334</v>
       </c>
       <c r="H5" t="n">
-        <v>87.09999999999999</v>
+        <v>88.5</v>
       </c>
       <c r="I5" t="n">
         <v>88.33942144013854</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>44</v>
+        <v>44.16666666666666</v>
       </c>
       <c r="K5" t="n">
-        <v>12.42</v>
+        <v>11.01</v>
       </c>
       <c r="L5" t="n">
         <v>4.63</v>
@@ -735,7 +794,19 @@
         <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>63</v>
+        <v>64</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>3</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -762,22 +833,22 @@
         <v>8.08</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>44728.38541666666</v>
+        <v>44728.55208333334</v>
       </c>
       <c r="H6" t="n">
-        <v>85.65000000000001</v>
+        <v>84.5</v>
       </c>
       <c r="I6" t="n">
         <v>85.25922382312585</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>14.83333333333333</v>
+        <v>15</v>
       </c>
       <c r="K6" t="n">
-        <v>-3.22</v>
+        <v>-4.52</v>
       </c>
       <c r="L6" t="n">
-        <v>3.84</v>
+        <v>5.31</v>
       </c>
       <c r="M6" t="n">
         <v>2.64</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S6" t="b">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -819,25 +902,25 @@
         <v>7.84</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>44735.55208333334</v>
+        <v>44736.38541666666</v>
       </c>
       <c r="H7" t="n">
-        <v>83</v>
+        <v>86.5</v>
       </c>
       <c r="I7" t="n">
         <v>85.7068871061052</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>7</v>
+        <v>7.833333333333333</v>
       </c>
       <c r="K7" t="n">
-        <v>1.78</v>
+        <v>-2.37</v>
       </c>
       <c r="L7" t="n">
-        <v>1.54</v>
+        <v>2.66</v>
       </c>
       <c r="M7" t="n">
-        <v>0.76</v>
+        <v>1.2</v>
       </c>
       <c r="N7" t="n">
         <v>5.92</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S7" t="b">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -876,19 +971,19 @@
         <v>10.17</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>44792.55208333334</v>
+        <v>44795.38541666666</v>
       </c>
       <c r="H8" t="n">
-        <v>105.25</v>
+        <v>103.55</v>
       </c>
       <c r="I8" t="n">
         <v>103.7145673032454</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>56.16666666666666</v>
+        <v>59</v>
       </c>
       <c r="K8" t="n">
-        <v>21.68</v>
+        <v>19.71</v>
       </c>
       <c r="L8" t="n">
         <v>4.68</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>78</v>
+        <v>79</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>3</v>
+      </c>
+      <c r="U8" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -933,25 +1040,25 @@
         <v>7.81</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>44797.55208333334</v>
+        <v>44798.38541666666</v>
       </c>
       <c r="H9" t="n">
-        <v>108.65</v>
+        <v>112.15</v>
       </c>
       <c r="I9" t="n">
         <v>110.522632762796</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>2.166666666666667</v>
+        <v>3</v>
       </c>
       <c r="K9" t="n">
-        <v>-4.93</v>
+        <v>-8.31</v>
       </c>
       <c r="L9" t="n">
-        <v>5.7</v>
+        <v>8.84</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>0.41</v>
       </c>
       <c r="N9" t="n">
         <v>4.83</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S9" t="b">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>8.51</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>44826.55208333334</v>
+        <v>44827.38541666666</v>
       </c>
       <c r="H10" t="n">
-        <v>122.6</v>
+        <v>116.7</v>
       </c>
       <c r="I10" t="n">
         <v>118.229347548789</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>28.16666666666667</v>
+        <v>29</v>
       </c>
       <c r="K10" t="n">
-        <v>9.32</v>
+        <v>4.06</v>
       </c>
       <c r="L10" t="n">
         <v>4.24</v>
@@ -1011,7 +1130,7 @@
         <v>3.5</v>
       </c>
       <c r="N10" t="n">
-        <v>2.06</v>
+        <v>5.06</v>
       </c>
       <c r="O10" t="n">
         <v>1.98</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S10" t="b">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -1047,22 +1178,22 @@
         <v>10.81</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>44851.55208333334</v>
+        <v>44852.38541666666</v>
       </c>
       <c r="H11" t="n">
-        <v>120.9</v>
+        <v>124.75</v>
       </c>
       <c r="I11" t="n">
         <v>121.2900145163301</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>24.16666666666667</v>
+        <v>25</v>
       </c>
       <c r="K11" t="n">
-        <v>-3.6</v>
+        <v>-6.9</v>
       </c>
       <c r="L11" t="n">
-        <v>5.44</v>
+        <v>7.28</v>
       </c>
       <c r="M11" t="n">
         <v>2.8</v>
@@ -1077,7 +1208,19 @@
         <v>1</v>
       </c>
       <c r="Q11" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>9.119999999999999</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>44911.55208333334</v>
+        <v>44914.38541666666</v>
       </c>
       <c r="H12" t="n">
-        <v>163.65</v>
+        <v>162.7</v>
       </c>
       <c r="I12" t="n">
         <v>163.0455091797592</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>59.16666666666666</v>
+        <v>62</v>
       </c>
       <c r="K12" t="n">
-        <v>31.18</v>
+        <v>30.42</v>
       </c>
       <c r="L12" t="n">
         <v>3.85</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>83</v>
+        <v>84</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>44861</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>3</v>
+      </c>
+      <c r="U12" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="13">
@@ -1161,22 +1316,22 @@
         <v>7.33</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>44924.38541666666</v>
+        <v>44924.55208333334</v>
       </c>
       <c r="H13" t="n">
-        <v>163.1</v>
+        <v>167.75</v>
       </c>
       <c r="I13" t="n">
         <v>164.0698297382796</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>10</v>
+        <v>10.16666666666667</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.25</v>
+        <v>-3.1</v>
       </c>
       <c r="L13" t="n">
-        <v>3.04</v>
+        <v>3.29</v>
       </c>
       <c r="M13" t="n">
         <v>0.5</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S13" t="b">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -1218,25 +1385,25 @@
         <v>8.92</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>44944.55208333334</v>
+        <v>44945.38541666666</v>
       </c>
       <c r="H14" t="n">
-        <v>159.8</v>
+        <v>158.6</v>
       </c>
       <c r="I14" t="n">
         <v>158.7542630282747</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>20</v>
+        <v>20.83333333333333</v>
       </c>
       <c r="K14" t="n">
-        <v>-4.74</v>
+        <v>-5.45</v>
       </c>
       <c r="L14" t="n">
-        <v>5.37</v>
+        <v>5.99</v>
       </c>
       <c r="M14" t="n">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="N14" t="n">
         <v>2.76</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S14" t="b">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1275,19 +1454,19 @@
         <v>6.05</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>44986.38541666666</v>
+        <v>44986.55208333334</v>
       </c>
       <c r="H15" t="n">
-        <v>145.7</v>
+        <v>146.85</v>
       </c>
       <c r="I15" t="n">
         <v>146.7727029853943</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>41</v>
+        <v>41.16666666666666</v>
       </c>
       <c r="K15" t="n">
-        <v>8.130000000000001</v>
+        <v>7.41</v>
       </c>
       <c r="L15" t="n">
         <v>3.03</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>55</v>
+        <v>56</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -1332,19 +1523,19 @@
         <v>6.99</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>44998.38541666666</v>
+        <v>44998.55208333334</v>
       </c>
       <c r="H16" t="n">
-        <v>148.65</v>
+        <v>146.45</v>
       </c>
       <c r="I16" t="n">
         <v>146.9466524012589</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>11.83333333333333</v>
+        <v>12</v>
       </c>
       <c r="K16" t="n">
-        <v>1.23</v>
+        <v>-0.27</v>
       </c>
       <c r="L16" t="n">
         <v>1.02</v>
@@ -1362,7 +1553,19 @@
         <v>1</v>
       </c>
       <c r="Q16" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S16" t="b">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1389,22 +1592,22 @@
         <v>6.82</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>45014.55208333334</v>
+        <v>45016.38541666666</v>
       </c>
       <c r="H17" t="n">
-        <v>147.1</v>
+        <v>151.1</v>
       </c>
       <c r="I17" t="n">
         <v>149.9769297278676</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>16</v>
+        <v>17.83333333333333</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.44</v>
+        <v>-3.18</v>
       </c>
       <c r="L17" t="n">
-        <v>2.73</v>
+        <v>3.65</v>
       </c>
       <c r="M17" t="n">
         <v>1.28</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>6.6</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>45051.55208333334</v>
+        <v>45054.38541666666</v>
       </c>
       <c r="H18" t="n">
-        <v>165.1</v>
+        <v>161.5</v>
       </c>
       <c r="I18" t="n">
         <v>162.8252963754958</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>35.16666666666666</v>
+        <v>38</v>
       </c>
       <c r="K18" t="n">
-        <v>9.27</v>
+        <v>6.88</v>
       </c>
       <c r="L18" t="n">
         <v>2.38</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -1503,22 +1730,22 @@
         <v>5.88</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>45062.38541666666</v>
+        <v>45062.55208333334</v>
       </c>
       <c r="H19" t="n">
-        <v>166</v>
+        <v>168.2</v>
       </c>
       <c r="I19" t="n">
         <v>166.5912503443778</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>8</v>
+        <v>8.166666666666666</v>
       </c>
       <c r="K19" t="n">
-        <v>-2.79</v>
+        <v>-4.15</v>
       </c>
       <c r="L19" t="n">
-        <v>3.22</v>
+        <v>4.89</v>
       </c>
       <c r="M19" t="n">
         <v>0.76</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S19" t="b">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>5.47</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>45139.55208333334</v>
+        <v>45140.38541666666</v>
       </c>
       <c r="H20" t="n">
-        <v>181.3</v>
+        <v>175.2</v>
       </c>
       <c r="I20" t="n">
         <v>176.6378897173684</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>77</v>
+        <v>77.83333333333333</v>
       </c>
       <c r="K20" t="n">
-        <v>7.79</v>
+        <v>4.16</v>
       </c>
       <c r="L20" t="n">
         <v>5.14</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>109</v>
+        <v>110</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>4</v>
+      </c>
+      <c r="U20" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="21">
@@ -1617,19 +1868,19 @@
         <v>6.74</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>45173.38541666666</v>
+        <v>45173.55208333334</v>
       </c>
       <c r="H21" t="n">
-        <v>173.7</v>
+        <v>176.35</v>
       </c>
       <c r="I21" t="n">
         <v>174.9193838974095</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>33</v>
+        <v>33.16666666666666</v>
       </c>
       <c r="K21" t="n">
-        <v>0.86</v>
+        <v>-0.66</v>
       </c>
       <c r="L21" t="n">
         <v>3.31</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1674,19 +1937,19 @@
         <v>5.23</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>45211.55208333334</v>
+        <v>45212.38541666666</v>
       </c>
       <c r="H22" t="n">
-        <v>187.45</v>
+        <v>183.95</v>
       </c>
       <c r="I22" t="n">
         <v>186.1374147571435</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>38</v>
+        <v>38.83333333333334</v>
       </c>
       <c r="K22" t="n">
-        <v>6.29</v>
+        <v>4.31</v>
       </c>
       <c r="L22" t="n">
         <v>1.93</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>53</v>
+        <v>54</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -1731,25 +2006,25 @@
         <v>5.15</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>45232.55208333334</v>
+        <v>45233.38541666666</v>
       </c>
       <c r="H23" t="n">
-        <v>180</v>
+        <v>182.9</v>
       </c>
       <c r="I23" t="n">
         <v>181.6179446647329</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>20.16666666666667</v>
+        <v>21</v>
       </c>
       <c r="K23" t="n">
-        <v>2.15</v>
+        <v>0.57</v>
       </c>
       <c r="L23" t="n">
         <v>2.34</v>
       </c>
       <c r="M23" t="n">
-        <v>0.68</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="N23" t="n">
         <v>4.13</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1788,22 +2075,22 @@
         <v>5.41</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>45236.55208333334</v>
+        <v>45237.38541666666</v>
       </c>
       <c r="H24" t="n">
-        <v>176.2</v>
+        <v>172.2</v>
       </c>
       <c r="I24" t="n">
         <v>174.2200899483818</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>3.166666666666667</v>
+        <v>4</v>
       </c>
       <c r="K24" t="n">
-        <v>-3.66</v>
+        <v>-5.85</v>
       </c>
       <c r="L24" t="n">
-        <v>4.18</v>
+        <v>5.99</v>
       </c>
       <c r="M24" t="n">
         <v>1.53</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S24" t="b">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -1845,28 +2144,28 @@
         <v>7.26</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>45260.55208333334</v>
+        <v>45261.38541666666</v>
       </c>
       <c r="H25" t="n">
-        <v>178.2</v>
+        <v>181.05</v>
       </c>
       <c r="I25" t="n">
         <v>180.5261426417026</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>23.16666666666667</v>
+        <v>24</v>
       </c>
       <c r="K25" t="n">
-        <v>-3.48</v>
+        <v>-5.14</v>
       </c>
       <c r="L25" t="n">
-        <v>5.6</v>
+        <v>6.71</v>
       </c>
       <c r="M25" t="n">
         <v>1.13</v>
       </c>
       <c r="N25" t="n">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="O25" t="n">
         <v>-2.07</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>4.37</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>45300.38541666666</v>
+        <v>45300.55208333334</v>
       </c>
       <c r="H26" t="n">
-        <v>204.2</v>
+        <v>202</v>
       </c>
       <c r="I26" t="n">
         <v>202.4542532674863</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>39</v>
+        <v>39.16666666666666</v>
       </c>
       <c r="K26" t="n">
-        <v>12.79</v>
+        <v>11.57</v>
       </c>
       <c r="L26" t="n">
         <v>1.35</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>53</v>
+        <v>54</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>45288</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -1959,25 +2282,25 @@
         <v>6.89</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>45320.55208333334</v>
+        <v>45321.38541666666</v>
       </c>
       <c r="H27" t="n">
-        <v>212.6</v>
+        <v>218.25</v>
       </c>
       <c r="I27" t="n">
         <v>213.6988952528465</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>20</v>
+        <v>20.83333333333333</v>
       </c>
       <c r="K27" t="n">
-        <v>-5.25</v>
+        <v>-8.039999999999999</v>
       </c>
       <c r="L27" t="n">
-        <v>5.77</v>
+        <v>8.84</v>
       </c>
       <c r="M27" t="n">
-        <v>0.49</v>
+        <v>0.52</v>
       </c>
       <c r="N27" t="n">
         <v>3.38</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -2016,19 +2351,19 @@
         <v>8.49</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>45363.55208333334</v>
+        <v>45364.38541666666</v>
       </c>
       <c r="H28" t="n">
-        <v>247.7</v>
+        <v>239.5</v>
       </c>
       <c r="I28" t="n">
         <v>241.9110412996738</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>42.16666666666666</v>
+        <v>43</v>
       </c>
       <c r="K28" t="n">
-        <v>13.49</v>
+        <v>9.74</v>
       </c>
       <c r="L28" t="n">
         <v>3.71</v>
@@ -2037,7 +2372,7 @@
         <v>1.45</v>
       </c>
       <c r="N28" t="n">
-        <v>4.54</v>
+        <v>4.6</v>
       </c>
       <c r="O28" t="n">
         <v>1.22</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>59</v>
+        <v>60</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -2073,19 +2420,19 @@
         <v>8.56</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>45383.38541666666</v>
+        <v>45383.55208333334</v>
       </c>
       <c r="H29" t="n">
-        <v>242</v>
+        <v>242.5</v>
       </c>
       <c r="I29" t="n">
         <v>242.2698500595912</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>19</v>
+        <v>19.16666666666667</v>
       </c>
       <c r="K29" t="n">
-        <v>-1.04</v>
+        <v>-1.25</v>
       </c>
       <c r="L29" t="n">
         <v>3.95</v>
@@ -2103,7 +2450,19 @@
         <v>1</v>
       </c>
       <c r="Q29" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -2130,28 +2489,28 @@
         <v>4.94</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>45397.55208333334</v>
+        <v>45398.38541666666</v>
       </c>
       <c r="H30" t="n">
-        <v>238.2</v>
+        <v>232.5</v>
       </c>
       <c r="I30" t="n">
         <v>235.1350710418789</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>14</v>
+        <v>14.83333333333333</v>
       </c>
       <c r="K30" t="n">
-        <v>-1.77</v>
+        <v>-4.12</v>
       </c>
       <c r="L30" t="n">
-        <v>2.54</v>
+        <v>4.33</v>
       </c>
       <c r="M30" t="n">
-        <v>0.99</v>
+        <v>1.26</v>
       </c>
       <c r="N30" t="n">
-        <v>2.2</v>
+        <v>2.43</v>
       </c>
       <c r="O30" t="n">
         <v>0.87</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S30" t="b">
+        <v>0</v>
+      </c>
+      <c r="T30" t="n">
+        <v>1</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -2187,22 +2558,22 @@
         <v>6.39</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>45407.55208333334</v>
+        <v>45408.38541666666</v>
       </c>
       <c r="H31" t="n">
-        <v>244.45</v>
+        <v>246.2</v>
       </c>
       <c r="I31" t="n">
         <v>245.2076265800162</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>10</v>
       </c>
       <c r="K31" t="n">
-        <v>-5.14</v>
+        <v>-5.89</v>
       </c>
       <c r="L31" t="n">
-        <v>5.48</v>
+        <v>6.77</v>
       </c>
       <c r="M31" t="n">
         <v>0.88</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -2244,28 +2627,28 @@
         <v>5.02</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>45415.55208333334</v>
+        <v>45418.38541666666</v>
       </c>
       <c r="H32" t="n">
-        <v>251.3</v>
+        <v>241.7</v>
       </c>
       <c r="I32" t="n">
         <v>243.5831495477389</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>10</v>
       </c>
       <c r="K32" t="n">
-        <v>2.07</v>
+        <v>-1.83</v>
       </c>
       <c r="L32" t="n">
-        <v>2.11</v>
+        <v>4.12</v>
       </c>
       <c r="M32" t="n">
         <v>0.04</v>
       </c>
       <c r="N32" t="n">
-        <v>1.32</v>
+        <v>4.24</v>
       </c>
       <c r="O32" t="n">
         <v>0.1</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S32" t="b">
+        <v>0</v>
+      </c>
+      <c r="T32" t="n">
+        <v>1</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -2301,28 +2696,28 @@
         <v>7.52</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>45443.55208333334</v>
+        <v>45446.38541666666</v>
       </c>
       <c r="H33" t="n">
-        <v>241.6</v>
+        <v>271.2</v>
       </c>
       <c r="I33" t="n">
         <v>252.0762068568595</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>25.16666666666667</v>
+        <v>28</v>
       </c>
       <c r="K33" t="n">
-        <v>0.04</v>
+        <v>-12.21</v>
       </c>
       <c r="L33" t="n">
-        <v>3.99</v>
+        <v>13.16</v>
       </c>
       <c r="M33" t="n">
-        <v>2.89</v>
+        <v>4.41</v>
       </c>
       <c r="N33" t="n">
-        <v>2.06</v>
+        <v>11.92</v>
       </c>
       <c r="O33" t="n">
         <v>-4.24</v>
@@ -2331,7 +2726,19 @@
         <v>1</v>
       </c>
       <c r="Q33" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -2358,28 +2765,28 @@
         <v>10.77</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>45446.55208333334</v>
+        <v>45447.38541666666</v>
       </c>
       <c r="H34" t="n">
-        <v>270.4</v>
+        <v>225.25</v>
       </c>
       <c r="I34" t="n">
         <v>250.7123396130931</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>0.1666666666666667</v>
+        <v>1</v>
       </c>
       <c r="K34" t="n">
-        <v>-0.29</v>
+        <v>-16.94</v>
       </c>
       <c r="L34" t="n">
-        <v>6.99</v>
+        <v>20.59</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>16.05</v>
       </c>
       <c r="O34" t="n">
         <v>11.92</v>
@@ -2388,7 +2795,19 @@
         <v>1</v>
       </c>
       <c r="Q34" t="n">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S34" t="b">
+        <v>0</v>
+      </c>
+      <c r="T34" t="n">
+        <v>1</v>
+      </c>
+      <c r="U34" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -2415,19 +2834,19 @@
         <v>22.15</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>45456.55208333334</v>
+        <v>45457.38541666666</v>
       </c>
       <c r="H35" t="n">
-        <v>257.8</v>
+        <v>261.35</v>
       </c>
       <c r="I35" t="n">
         <v>261.1473544220552</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>10</v>
       </c>
       <c r="K35" t="n">
-        <v>-14.45</v>
+        <v>-16.03</v>
       </c>
       <c r="L35" t="n">
         <v>18.22</v>
@@ -2445,7 +2864,19 @@
         <v>1</v>
       </c>
       <c r="Q35" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S35" t="b">
+        <v>0</v>
+      </c>
+      <c r="T35" t="n">
+        <v>1</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -2472,19 +2903,19 @@
         <v>8.32</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>45482.38541666666</v>
+        <v>45482.55208333334</v>
       </c>
       <c r="H36" t="n">
-        <v>246.1</v>
+        <v>245.25</v>
       </c>
       <c r="I36" t="n">
         <v>245.6400801325063</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>25</v>
+        <v>25.16666666666667</v>
       </c>
       <c r="K36" t="n">
-        <v>-5.84</v>
+        <v>-6.16</v>
       </c>
       <c r="L36" t="n">
         <v>6.45</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -2529,19 +2972,19 @@
         <v>4.98</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>45523.55208333334</v>
+        <v>45524.38541666666</v>
       </c>
       <c r="H37" t="n">
-        <v>231.45</v>
+        <v>237.5</v>
       </c>
       <c r="I37" t="n">
         <v>236.1397146710924</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>41</v>
+        <v>41.83333333333334</v>
       </c>
       <c r="K37" t="n">
-        <v>5.63</v>
+        <v>3.16</v>
       </c>
       <c r="L37" t="n">
         <v>0.61</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>55</v>
+        <v>56</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -2586,22 +3041,22 @@
         <v>6.16</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>45539.38541666666</v>
+        <v>45539.55208333334</v>
       </c>
       <c r="H38" t="n">
-        <v>230.05</v>
+        <v>227.95</v>
       </c>
       <c r="I38" t="n">
         <v>228.3971323233397</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>15</v>
+        <v>15.16666666666667</v>
       </c>
       <c r="K38" t="n">
-        <v>-3.14</v>
+        <v>-4.02</v>
       </c>
       <c r="L38" t="n">
-        <v>3.6</v>
+        <v>4.44</v>
       </c>
       <c r="M38" t="n">
         <v>1.13</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -2643,22 +3110,22 @@
         <v>4.47</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>45558.55208333334</v>
+        <v>45559.38541666666</v>
       </c>
       <c r="H39" t="n">
-        <v>228.65</v>
+        <v>229.55</v>
       </c>
       <c r="I39" t="n">
         <v>228.8119912421971</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>19</v>
+        <v>19.83333333333333</v>
       </c>
       <c r="K39" t="n">
-        <v>-0.31</v>
+        <v>-0.7</v>
       </c>
       <c r="L39" t="n">
-        <v>1.1</v>
+        <v>1.51</v>
       </c>
       <c r="M39" t="n">
         <v>0.9399999999999999</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S39" t="b">
+        <v>0</v>
+      </c>
+      <c r="T39" t="n">
+        <v>1</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -2700,28 +3179,28 @@
         <v>5.16</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>45586.55208333334</v>
+        <v>45587.38541666666</v>
       </c>
       <c r="H40" t="n">
-        <v>229.6</v>
+        <v>220.9</v>
       </c>
       <c r="I40" t="n">
         <v>223.560846169661</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>27.16666666666667</v>
+        <v>28</v>
       </c>
       <c r="K40" t="n">
-        <v>0.02</v>
+        <v>-3.77</v>
       </c>
       <c r="L40" t="n">
-        <v>2.96</v>
+        <v>4.01</v>
       </c>
       <c r="M40" t="n">
         <v>1.01</v>
       </c>
       <c r="N40" t="n">
-        <v>2.73</v>
+        <v>4.81</v>
       </c>
       <c r="O40" t="n">
         <v>-0.17</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -2757,28 +3248,28 @@
         <v>8.039999999999999</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>45590.55208333334</v>
+        <v>45593.38541666666</v>
       </c>
       <c r="H41" t="n">
-        <v>223.3</v>
+        <v>236.5</v>
       </c>
       <c r="I41" t="n">
         <v>231.3627828973753</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>3.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K41" t="n">
-        <v>-1.09</v>
+        <v>-7.06</v>
       </c>
       <c r="L41" t="n">
-        <v>4.23</v>
+        <v>7.49</v>
       </c>
       <c r="M41" t="n">
-        <v>0.11</v>
+        <v>0.65</v>
       </c>
       <c r="N41" t="n">
-        <v>3.03</v>
+        <v>4.75</v>
       </c>
       <c r="O41" t="n">
         <v>-4.81</v>
@@ -2787,7 +3278,19 @@
         <v>1</v>
       </c>
       <c r="Q41" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S41" t="b">
+        <v>0</v>
+      </c>
+      <c r="T41" t="n">
+        <v>1</v>
+      </c>
+      <c r="U41" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -2814,28 +3317,28 @@
         <v>10.31</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>45608.55208333334</v>
+        <v>45609.38541666666</v>
       </c>
       <c r="H42" t="n">
-        <v>236.65</v>
+        <v>232.45</v>
       </c>
       <c r="I42" t="n">
         <v>233.6184412062445</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>15.16666666666667</v>
+        <v>16</v>
       </c>
       <c r="K42" t="n">
-        <v>0.06</v>
+        <v>-1.71</v>
       </c>
       <c r="L42" t="n">
         <v>5.01</v>
       </c>
       <c r="M42" t="n">
-        <v>0.1</v>
+        <v>1.01</v>
       </c>
       <c r="N42" t="n">
-        <v>2.66</v>
+        <v>3.27</v>
       </c>
       <c r="O42" t="n">
         <v>4.75</v>
@@ -2844,7 +3347,19 @@
         <v>1</v>
       </c>
       <c r="Q42" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -2871,19 +3386,19 @@
         <v>6.79</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>45621.38541666666</v>
+        <v>45621.55208333334</v>
       </c>
       <c r="H43" t="n">
-        <v>231.35</v>
+        <v>232.25</v>
       </c>
       <c r="I43" t="n">
         <v>231.3549756579355</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>12</v>
+        <v>12.16666666666667</v>
       </c>
       <c r="K43" t="n">
-        <v>0.47</v>
+        <v>0.09</v>
       </c>
       <c r="L43" t="n">
         <v>1.85</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S43" t="b">
+        <v>0</v>
+      </c>
+      <c r="T43" t="n">
+        <v>1</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -2928,19 +3455,19 @@
         <v>7.52</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>45643.55208333334</v>
+        <v>45644.38541666666</v>
       </c>
       <c r="H44" t="n">
-        <v>239.35</v>
+        <v>236.15</v>
       </c>
       <c r="I44" t="n">
         <v>236.4221126912103</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>22</v>
+        <v>22.83333333333333</v>
       </c>
       <c r="K44" t="n">
-        <v>3.06</v>
+        <v>1.68</v>
       </c>
       <c r="L44" t="n">
         <v>1.53</v>
@@ -2958,7 +3485,19 @@
         <v>1</v>
       </c>
       <c r="Q44" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>2</v>
+      </c>
+      <c r="U44" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="45">
@@ -2985,19 +3524,19 @@
         <v>4.81</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>45674.55208333334</v>
+        <v>45677.38541666666</v>
       </c>
       <c r="H45" t="n">
-        <v>213.4</v>
+        <v>220.3</v>
       </c>
       <c r="I45" t="n">
         <v>216.8867893040296</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>30.16666666666667</v>
+        <v>33</v>
       </c>
       <c r="K45" t="n">
-        <v>9.630000000000001</v>
+        <v>6.71</v>
       </c>
       <c r="L45" t="n">
         <v>1.44</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>2</v>
+      </c>
+      <c r="U45" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="46">
@@ -3042,28 +3593,28 @@
         <v>7.58</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45687.55208333334</v>
+        <v>45688.38541666666</v>
       </c>
       <c r="H46" t="n">
-        <v>208.4</v>
+        <v>202</v>
       </c>
       <c r="I46" t="n">
         <v>205.8893741230311</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>10.16666666666667</v>
+        <v>11</v>
       </c>
       <c r="K46" t="n">
-        <v>-5.4</v>
+        <v>-8.31</v>
       </c>
       <c r="L46" t="n">
-        <v>7.15</v>
+        <v>10.28</v>
       </c>
       <c r="M46" t="n">
-        <v>0.88</v>
+        <v>1.82</v>
       </c>
       <c r="N46" t="n">
-        <v>2.25</v>
+        <v>3.98</v>
       </c>
       <c r="O46" t="n">
         <v>1.64</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>2</v>
+      </c>
+      <c r="U46" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -3099,19 +3662,19 @@
         <v>6.15</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45721.55208333334</v>
+        <v>45722.38541666666</v>
       </c>
       <c r="H47" t="n">
-        <v>191.95</v>
+        <v>195.05</v>
       </c>
       <c r="I47" t="n">
         <v>193.1977924870817</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>33.16666666666666</v>
+        <v>34</v>
       </c>
       <c r="K47" t="n">
-        <v>4.98</v>
+        <v>3.44</v>
       </c>
       <c r="L47" t="n">
         <v>3.17</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>2</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -3156,19 +3731,19 @@
         <v>6.19</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45783.38541666666</v>
+        <v>45783.55208333334</v>
       </c>
       <c r="H48" t="n">
-        <v>228</v>
+        <v>207.85</v>
       </c>
       <c r="I48" t="n">
         <v>226.3914922712312</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>61</v>
+        <v>61.16666666666666</v>
       </c>
       <c r="K48" t="n">
-        <v>16.89</v>
+        <v>6.56</v>
       </c>
       <c r="L48" t="n">
         <v>3.46</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>73</v>
+        <v>74</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>3</v>
+      </c>
+      <c r="U48" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="49">
@@ -3213,19 +3800,19 @@
         <v>13.32</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45791.55208333334</v>
+        <v>45792.38541666666</v>
       </c>
       <c r="H49" t="n">
-        <v>219.05</v>
+        <v>219.75</v>
       </c>
       <c r="I49" t="n">
         <v>219.4952706552035</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>8</v>
+        <v>8.833333333333334</v>
       </c>
       <c r="K49" t="n">
-        <v>-5.39</v>
+        <v>-5.73</v>
       </c>
       <c r="L49" t="n">
         <v>9.84</v>
@@ -3243,7 +3830,19 @@
         <v>1</v>
       </c>
       <c r="Q49" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S49" t="b">
+        <v>0</v>
+      </c>
+      <c r="T49" t="n">
+        <v>1</v>
+      </c>
+      <c r="U49" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -3270,25 +3869,25 @@
         <v>6.43</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45820.55208333334</v>
+        <v>45821.38541666666</v>
       </c>
       <c r="H50" t="n">
-        <v>232.5</v>
+        <v>230.1</v>
       </c>
       <c r="I50" t="n">
         <v>230.1541465345513</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>28.16666666666667</v>
+        <v>29</v>
       </c>
       <c r="K50" t="n">
-        <v>5.8</v>
+        <v>4.71</v>
       </c>
       <c r="L50" t="n">
         <v>0.75</v>
       </c>
       <c r="M50" t="n">
-        <v>0.53</v>
+        <v>2.09</v>
       </c>
       <c r="N50" t="n">
         <v>1.44</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>2</v>
+      </c>
+      <c r="U50" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -3327,28 +3938,28 @@
         <v>4.37</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45835.55208333334</v>
+        <v>45838.38541666666</v>
       </c>
       <c r="H51" t="n">
-        <v>234.4</v>
+        <v>240.7</v>
       </c>
       <c r="I51" t="n">
         <v>235.3161847217258</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>17</v>
       </c>
       <c r="K51" t="n">
-        <v>-1.87</v>
+        <v>-4.61</v>
       </c>
       <c r="L51" t="n">
-        <v>3.17</v>
+        <v>5.11</v>
       </c>
       <c r="M51" t="n">
         <v>0.97</v>
       </c>
       <c r="N51" t="n">
-        <v>1.57</v>
+        <v>2.69</v>
       </c>
       <c r="O51" t="n">
         <v>-0.09</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>2</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -3384,19 +4007,19 @@
         <v>5.83</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45849.38541666666</v>
+        <v>45849.55208333334</v>
       </c>
       <c r="H52" t="n">
-        <v>230.5</v>
+        <v>229.55</v>
       </c>
       <c r="I52" t="n">
         <v>229.7522186391357</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>11</v>
+        <v>11.16666666666667</v>
       </c>
       <c r="K52" t="n">
-        <v>-4.24</v>
+        <v>-4.63</v>
       </c>
       <c r="L52" t="n">
         <v>5.03</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S52" t="b">
+        <v>0</v>
+      </c>
+      <c r="T52" t="n">
+        <v>1</v>
+      </c>
+      <c r="U52" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -3441,28 +4076,28 @@
         <v>3.86</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>45853.55208333334</v>
+        <v>45854.38541666666</v>
       </c>
       <c r="H53" t="n">
-        <v>236.85</v>
+        <v>242</v>
       </c>
       <c r="I53" t="n">
         <v>238.4072955734373</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>4</v>
+        <v>4.833333333333333</v>
       </c>
       <c r="K53" t="n">
-        <v>-3.18</v>
+        <v>-5.42</v>
       </c>
       <c r="L53" t="n">
-        <v>3.51</v>
+        <v>5.49</v>
       </c>
       <c r="M53" t="n">
         <v>0.2</v>
       </c>
       <c r="N53" t="n">
-        <v>1.68</v>
+        <v>1.84</v>
       </c>
       <c r="O53" t="n">
         <v>-0.65</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S53" t="b">
+        <v>0</v>
+      </c>
+      <c r="T53" t="n">
+        <v>1</v>
+      </c>
+      <c r="U53" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -3498,22 +4145,22 @@
         <v>5.25</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>45860.38541666666</v>
+        <v>45860.55208333334</v>
       </c>
       <c r="H54" t="n">
-        <v>233.85</v>
+        <v>231.85</v>
       </c>
       <c r="I54" t="n">
         <v>232.8336565831569</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>6</v>
+        <v>6.166666666666667</v>
       </c>
       <c r="K54" t="n">
-        <v>-3.37</v>
+        <v>-4.19</v>
       </c>
       <c r="L54" t="n">
-        <v>3.62</v>
+        <v>4.4</v>
       </c>
       <c r="M54" t="n">
         <v>0.57</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S54" t="b">
+        <v>0</v>
+      </c>
+      <c r="T54" t="n">
+        <v>1</v>
+      </c>
+      <c r="U54" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -3555,19 +4214,19 @@
         <v>4.16</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>45916.55208333334</v>
+        <v>45917.38541666666</v>
       </c>
       <c r="H55" t="n">
-        <v>232.7</v>
+        <v>235.4</v>
       </c>
       <c r="I55" t="n">
         <v>233.7941611764084</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>56</v>
+        <v>56.83333333333334</v>
       </c>
       <c r="K55" t="n">
-        <v>-0.37</v>
+        <v>-1.53</v>
       </c>
       <c r="L55" t="n">
         <v>4.03</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>77</v>
+        <v>78</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>3</v>
+      </c>
+      <c r="U55" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="56">
@@ -3612,19 +4283,19 @@
         <v>3.84</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>45996.55208333334</v>
+        <v>45999.38541666666</v>
       </c>
       <c r="H56" t="n">
-        <v>282.8</v>
+        <v>275.5</v>
       </c>
       <c r="I56" t="n">
         <v>277.7247089910875</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>79.16666666666667</v>
+        <v>82</v>
       </c>
       <c r="K56" t="n">
-        <v>20.14</v>
+        <v>17.03</v>
       </c>
       <c r="L56" t="n">
         <v>1.32</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>109</v>
+        <v>110</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>4</v>
+      </c>
+      <c r="U56" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="57">
@@ -3669,22 +4352,22 @@
         <v>6.85</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>46010.55208333334</v>
+        <v>46013.38541666666</v>
       </c>
       <c r="H57" t="n">
-        <v>282.55</v>
+        <v>285.25</v>
       </c>
       <c r="I57" t="n">
         <v>284.4174454870223</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K57" t="n">
-        <v>-2.56</v>
+        <v>-3.54</v>
       </c>
       <c r="L57" t="n">
-        <v>3.12</v>
+        <v>3.99</v>
       </c>
       <c r="M57" t="n">
         <v>1</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S57" t="b">
+        <v>0</v>
+      </c>
+      <c r="T57" t="n">
+        <v>1</v>
+      </c>
+      <c r="U57" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -3726,19 +4421,19 @@
         <v>4.01</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>46045.38541666666</v>
+        <v>46045.55208333334</v>
       </c>
       <c r="H58" t="n">
-        <v>288.75</v>
+        <v>286.8</v>
       </c>
       <c r="I58" t="n">
         <v>287.6553526153382</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>32</v>
+        <v>32.16666666666666</v>
       </c>
       <c r="K58" t="n">
-        <v>1.23</v>
+        <v>0.54</v>
       </c>
       <c r="L58" t="n">
         <v>3.05</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>2</v>
+      </c>
+      <c r="U58" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="59">
@@ -3783,19 +4490,19 @@
         <v>5.61</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>46069.55208333334</v>
+        <v>46070.38541666666</v>
       </c>
       <c r="H59" t="n">
-        <v>284.1</v>
+        <v>294.4</v>
       </c>
       <c r="I59" t="n">
         <v>288.4869391077187</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>24</v>
+        <v>24.83333333333333</v>
       </c>
       <c r="K59" t="n">
-        <v>0.9399999999999999</v>
+        <v>-2.65</v>
       </c>
       <c r="L59" t="n">
         <v>4.45</v>
@@ -3804,7 +4511,7 @@
         <v>4.17</v>
       </c>
       <c r="N59" t="n">
-        <v>2.65</v>
+        <v>3.48</v>
       </c>
       <c r="O59" t="n">
         <v>-2.93</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>2</v>
+      </c>
+      <c r="U59" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="60">
@@ -3840,19 +4559,19 @@
         <v>7.38</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>46083.55208333334</v>
+        <v>46085.38541666666</v>
       </c>
       <c r="H60" t="n">
-        <v>305.9</v>
+        <v>289.85</v>
       </c>
       <c r="I60" t="n">
         <v>297.561739165656</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>13.16666666666667</v>
+        <v>15</v>
       </c>
       <c r="K60" t="n">
-        <v>3.91</v>
+        <v>-1.55</v>
       </c>
       <c r="L60" t="n">
         <v>4.18</v>
@@ -3861,7 +4580,7 @@
         <v>2.63</v>
       </c>
       <c r="N60" t="n">
-        <v>1.43</v>
+        <v>5</v>
       </c>
       <c r="O60" t="n">
         <v>3.48</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S60" t="b">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>2</v>
+      </c>
+      <c r="U60" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="61">
@@ -3897,28 +4628,28 @@
         <v>8.1</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>46119.55208333334</v>
+        <v>46120.38541666666</v>
       </c>
       <c r="H61" t="n">
-        <v>249.9</v>
+        <v>265.25</v>
       </c>
       <c r="I61" t="n">
         <v>258.2245342769449</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>34.16666666666666</v>
+        <v>35</v>
       </c>
       <c r="K61" t="n">
-        <v>13.78</v>
+        <v>8.49</v>
       </c>
       <c r="L61" t="n">
         <v>3.73</v>
       </c>
       <c r="M61" t="n">
-        <v>2.38</v>
+        <v>3.88</v>
       </c>
       <c r="N61" t="n">
-        <v>4.13</v>
+        <v>7.14</v>
       </c>
       <c r="O61" t="n">
         <v>-5</v>
@@ -3927,7 +4658,19 @@
         <v>1</v>
       </c>
       <c r="Q61" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>2</v>
+      </c>
+      <c r="U61" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="62">
@@ -3954,22 +4697,22 @@
         <v>9.32</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>46139.55208333334</v>
+        <v>46140.38541666666</v>
       </c>
       <c r="H62" t="n">
-        <v>265.5</v>
+        <v>260.2</v>
       </c>
       <c r="I62" t="n">
         <v>260.8143260090699</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>19.16666666666667</v>
+        <v>20</v>
       </c>
       <c r="K62" t="n">
-        <v>0.09</v>
+        <v>-1.9</v>
       </c>
       <c r="L62" t="n">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="M62" t="n">
         <v>2.33</v>
@@ -3984,7 +4727,19 @@
         <v>1</v>
       </c>
       <c r="Q62" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S62" t="b">
+        <v>0</v>
+      </c>
+      <c r="T62" t="n">
+        <v>1</v>
+      </c>
+      <c r="U62" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -4011,28 +4766,28 @@
         <v>5.71</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>46181.55208333334</v>
+        <v>46182.38541666666</v>
       </c>
       <c r="H63" t="n">
-        <v>259.25</v>
+        <v>271.85</v>
       </c>
       <c r="I63" t="n">
         <v>264.4188433506002</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>41.16666666666666</v>
+        <v>42</v>
       </c>
       <c r="K63" t="n">
-        <v>0.37</v>
+        <v>-4.48</v>
       </c>
       <c r="L63" t="n">
-        <v>3.54</v>
+        <v>4.53</v>
       </c>
       <c r="M63" t="n">
         <v>2.1</v>
       </c>
       <c r="N63" t="n">
-        <v>3</v>
+        <v>5.57</v>
       </c>
       <c r="O63" t="n">
         <v>-1.98</v>
@@ -4041,7 +4796,19 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S63" t="b">
+        <v>1</v>
+      </c>
+      <c r="T63" t="n">
+        <v>2</v>
+      </c>
+      <c r="U63" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="64">
@@ -4068,19 +4835,19 @@
         <v>7.68</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>46204.38541666666</v>
+        <v>46204.55208333334</v>
       </c>
       <c r="H64" t="n">
-        <v>272.7</v>
+        <v>271.15</v>
       </c>
       <c r="I64" t="n">
         <v>272.3339538582794</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>22</v>
+        <v>22.16666666666667</v>
       </c>
       <c r="K64" t="n">
-        <v>0.31</v>
+        <v>-0.26</v>
       </c>
       <c r="L64" t="n">
         <v>4.21</v>
@@ -4098,7 +4865,19 @@
         <v>1</v>
       </c>
       <c r="Q64" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S64" t="b">
+        <v>1</v>
+      </c>
+      <c r="T64" t="n">
+        <v>2</v>
+      </c>
+      <c r="U64" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -4125,19 +4904,19 @@
         <v>4.51</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>46294.55208333334</v>
+        <v>46295.38541666666</v>
       </c>
       <c r="H65" t="n">
-        <v>230.08</v>
+        <v>234.77</v>
       </c>
       <c r="I65" t="n">
         <v>234.6719870486721</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>90</v>
+        <v>90.83333333333333</v>
       </c>
       <c r="K65" t="n">
-        <v>15.15</v>
+        <v>13.42</v>
       </c>
       <c r="L65" t="n">
         <v>0.87</v>
@@ -4155,7 +4934,19 @@
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>127</v>
+        <v>128</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S65" t="b">
+        <v>1</v>
+      </c>
+      <c r="T65" t="n">
+        <v>4</v>
+      </c>
+      <c r="U65" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="66">
@@ -4206,6 +4997,12 @@
       <c r="Q66" t="n">
         <v>36</v>
       </c>
+      <c r="R66" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S66" t="inlineStr"/>
+      <c r="T66" t="inlineStr"/>
+      <c r="U66" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6308,7 +7105,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>25.9</v>
+        <v>26.9</v>
       </c>
     </row>
     <row r="6">
@@ -6318,7 +7115,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>21.1</v>
+        <v>21.6</v>
       </c>
     </row>
     <row r="7">
@@ -6328,7 +7125,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>90</v>
+        <v>90.8</v>
       </c>
     </row>
     <row r="8">
@@ -6338,7 +7135,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -6348,7 +7145,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>34.4</v>
+        <v>38.2</v>
       </c>
     </row>
     <row r="10">
@@ -6358,7 +7155,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>52.4</v>
+        <v>53</v>
       </c>
     </row>
     <row r="11">
@@ -6398,7 +7195,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.98</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="15">
@@ -6408,7 +7205,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5.16</v>
+        <v>2.27</v>
       </c>
     </row>
     <row r="16">
@@ -6418,7 +7215,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.8</v>
+        <v>-1.82</v>
       </c>
     </row>
     <row r="17">
@@ -6428,7 +7225,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>31.18</v>
+        <v>30.42</v>
       </c>
     </row>
     <row r="18">
@@ -6438,7 +7235,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>57.8</v>
+        <v>39.1</v>
       </c>
     </row>
     <row r="19">
@@ -6448,7 +7245,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3.84</v>
+        <v>4.79</v>
       </c>
     </row>
     <row r="20">
@@ -6458,7 +7255,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3.57</v>
+        <v>4.15</v>
       </c>
     </row>
     <row r="21">
@@ -6468,7 +7265,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>18.22</v>
+        <v>20.59</v>
       </c>
     </row>
     <row r="22">
@@ -6478,7 +7275,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
     </row>
     <row r="23">
@@ -6488,7 +7285,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="24">
@@ -6498,7 +7295,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.57</v>
+        <v>1.72</v>
       </c>
     </row>
     <row r="25">
@@ -6518,7 +7315,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3.39</v>
+        <v>4.21</v>
       </c>
     </row>
     <row r="27">
@@ -6528,7 +7325,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>11.04</v>
+        <v>16.05</v>
       </c>
     </row>
     <row r="28">
@@ -6538,7 +7335,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
     </row>
     <row r="29">
